--- a/Extra files/inventory_simulation_daily_detailed_5s.xlsx
+++ b/Extra files/inventory_simulation_daily_detailed_5s.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kristineandersen/Desktop/Speciale/Thesis_project/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kristineandersen/Desktop/Speciale/Thesis_project/Extra files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C73D7D1-C2E8-754A-85DD-A227A32518E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B684BB8D-9A2A-0540-AE94-0AC863786E43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17180" activeTab="1" xr2:uid="{14B89E8B-456D-DB47-AC1D-EA51CAA3418A}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17180" xr2:uid="{14B89E8B-456D-DB47-AC1D-EA51CAA3418A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
@@ -21,7 +21,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="4" r:id="rId3"/>
+    <pivotCache cacheId="2" r:id="rId3"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -4335,7 +4335,7 @@
     <t>Grand Total</t>
   </si>
   <si>
-    <t>Average of ordered_today</t>
+    <t>StdDev of ordered_today</t>
   </si>
 </sst>
 </file>
@@ -23122,7 +23122,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8C843AE4-18BE-AF4E-87DD-9A29B7CD782C}" name="PivotTable1" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8C843AE4-18BE-AF4E-87DD-9A29B7CD782C}" name="PivotTable1" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:B12" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="23">
     <pivotField numFmtId="14" showAll="0"/>
@@ -23337,7 +23337,7 @@
     <i/>
   </colItems>
   <dataFields count="1">
-    <dataField name="Average of ordered_today" fld="14" subtotal="average" baseField="0" baseItem="0"/>
+    <dataField name="StdDev of ordered_today" fld="14" subtotal="stdDev" baseField="0" baseItem="0"/>
   </dataFields>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
@@ -23672,7 +23672,7 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.1640625" bestFit="1" customWidth="1"/>
     <col min="3" max="76" width="3.1640625" bestFit="1" customWidth="1"/>
     <col min="77" max="137" width="4.1640625" bestFit="1" customWidth="1"/>
     <col min="138" max="138" width="10.5" bestFit="1" customWidth="1"/>
@@ -23691,7 +23691,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="5">
-        <v>99.888888888888886</v>
+        <v>40.140608048233368</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
@@ -23699,7 +23699,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="5">
-        <v>99.922222222222217</v>
+        <v>36.852340580242618</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
@@ -23707,7 +23707,7 @@
         <v>3</v>
       </c>
       <c r="B6" s="5">
-        <v>99.566666666666663</v>
+        <v>41.0573865310987</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
@@ -23715,7 +23715,7 @@
         <v>4</v>
       </c>
       <c r="B7" s="5">
-        <v>97.3</v>
+        <v>37.619457671604174</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
@@ -23723,7 +23723,7 @@
         <v>5</v>
       </c>
       <c r="B8" s="5">
-        <v>94.911111111111111</v>
+        <v>39.857793408325733</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
@@ -23731,7 +23731,7 @@
         <v>6</v>
       </c>
       <c r="B9" s="5">
-        <v>92.733333333333334</v>
+        <v>39.485113109922459</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
@@ -23739,7 +23739,7 @@
         <v>7</v>
       </c>
       <c r="B10" s="5">
-        <v>93.644444444444446</v>
+        <v>42.611469445908291</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
@@ -23747,7 +23747,7 @@
         <v>8</v>
       </c>
       <c r="B11" s="5">
-        <v>95.37777777777778</v>
+        <v>40.197427884000099</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
@@ -23755,7 +23755,7 @@
         <v>1430</v>
       </c>
       <c r="B12" s="5">
-        <v>96.668055555555554</v>
+        <v>39.6636706159236</v>
       </c>
     </row>
   </sheetData>
